--- a/project/outputs_xlsx_solution/test33.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/test33.2-wide.xlsx
@@ -137,6 +137,9 @@
     <t>bne X4, X0, 68</t>
   </si>
   <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
     <t>fadd F23, F23, F21</t>
   </si>
   <si>
@@ -149,64 +152,61 @@
     <t>bne X1, X0, 36</t>
   </si>
   <si>
+    <t>fsd F10, 136(X0)</t>
+  </si>
+  <si>
+    <t>fsd F11, 140(X0)</t>
+  </si>
+  <si>
+    <t>fsd F12, 144(X0)</t>
+  </si>
+  <si>
+    <t>fsd F13, 148(X0)</t>
+  </si>
+  <si>
+    <t>fsd F14, 152(X0)</t>
+  </si>
+  <si>
+    <t>fsd F20, 156(X0)</t>
+  </si>
+  <si>
+    <t>fsd F21, 160(X0)</t>
+  </si>
+  <si>
+    <t>fsd F22, 164(X0)</t>
+  </si>
+  <si>
+    <t>fsd F23, 168(X0)</t>
+  </si>
+  <si>
+    <t>[Legend]</t>
+  </si>
+  <si>
+    <t>Instruction Fetch</t>
+  </si>
+  <si>
+    <t>Instruction Decode</t>
+  </si>
+  <si>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
     <t>CDB Stall</t>
-  </si>
-  <si>
-    <t>fsd F10, 136(X0)</t>
-  </si>
-  <si>
-    <t>fsd F11, 140(X0)</t>
-  </si>
-  <si>
-    <t>fsd F12, 144(X0)</t>
-  </si>
-  <si>
-    <t>fsd F13, 148(X0)</t>
-  </si>
-  <si>
-    <t>fsd F14, 152(X0)</t>
-  </si>
-  <si>
-    <t>fsd F20, 156(X0)</t>
-  </si>
-  <si>
-    <t>fsd F21, 160(X0)</t>
-  </si>
-  <si>
-    <t>fsd F22, 164(X0)</t>
-  </si>
-  <si>
-    <t>fsd F23, 168(X0)</t>
-  </si>
-  <si>
-    <t>[Legend]</t>
-  </si>
-  <si>
-    <t>Instruction Fetch</t>
-  </si>
-  <si>
-    <t>Instruction Decode</t>
-  </si>
-  <si>
-    <t>Add to Issue Queue</t>
-  </si>
-  <si>
-    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
-  </si>
-  <si>
-    <t>Write Back</t>
-  </si>
-  <si>
-    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
-  </si>
-  <si>
-    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
-  </si>
-  <si>
-    <t>ROB Stall</t>
-  </si>
-  <si>
-    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
@@ -846,27 +846,6 @@
       <c r="CN1">
         <v>89</v>
       </c>
-      <c r="CO1">
-        <v>90</v>
-      </c>
-      <c r="CP1">
-        <v>91</v>
-      </c>
-      <c r="CQ1">
-        <v>92</v>
-      </c>
-      <c r="CR1">
-        <v>93</v>
-      </c>
-      <c r="CS1">
-        <v>94</v>
-      </c>
-      <c r="CT1">
-        <v>95</v>
-      </c>
-      <c r="CU1">
-        <v>96</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1189,18 +1168,27 @@
         <v>26</v>
       </c>
       <c r="R13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U13" t="s">
         <v>10</v>
       </c>
       <c r="V13" t="s">
+        <v>10</v>
+      </c>
+      <c r="W13" t="s">
+        <v>10</v>
+      </c>
+      <c r="X13" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1235,7 +1223,7 @@
       <c r="Q14" t="s">
         <v>14</v>
       </c>
-      <c r="V14" t="s">
+      <c r="Y14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1276,7 +1264,7 @@
       <c r="T15" t="s">
         <v>14</v>
       </c>
-      <c r="W15" t="s">
+      <c r="Z15" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1302,7 +1290,7 @@
       <c r="O16" t="s">
         <v>14</v>
       </c>
-      <c r="W16" t="s">
+      <c r="Z16" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1328,7 +1316,7 @@
       <c r="P17" t="s">
         <v>14</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AA17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1354,7 +1342,7 @@
       <c r="P18" t="s">
         <v>14</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AA18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1375,15 +1363,12 @@
         <v>7</v>
       </c>
       <c r="P19" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>10</v>
-      </c>
-      <c r="R19" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y19" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB19" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1407,33 +1392,21 @@
         <v>16</v>
       </c>
       <c r="Q20" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="R20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U20" t="s">
-        <v>11</v>
-      </c>
-      <c r="V20" t="s">
-        <v>10</v>
-      </c>
-      <c r="W20" t="s">
-        <v>10</v>
-      </c>
-      <c r="X20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z20" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB20" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1456,14 +1429,17 @@
       <c r="Q21" t="s">
         <v>26</v>
       </c>
-      <c r="Z21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>10</v>
+      <c r="U21" t="s">
+        <v>10</v>
+      </c>
+      <c r="V21" t="s">
+        <v>10</v>
+      </c>
+      <c r="W21" t="s">
+        <v>10</v>
+      </c>
+      <c r="X21" t="s">
+        <v>14</v>
       </c>
       <c r="AC21" t="s">
         <v>15</v>
@@ -1488,10 +1464,13 @@
       <c r="R22" t="s">
         <v>26</v>
       </c>
+      <c r="X22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>14</v>
+      </c>
       <c r="AC22" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1512,12 +1491,9 @@
         <v>7</v>
       </c>
       <c r="R23" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="S23" t="s">
-        <v>10</v>
-      </c>
-      <c r="T23" t="s">
         <v>14</v>
       </c>
       <c r="AD23" t="s">
@@ -1541,15 +1517,12 @@
         <v>7</v>
       </c>
       <c r="S24" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T24" t="s">
-        <v>10</v>
-      </c>
-      <c r="U24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE24" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1563,16 +1536,16 @@
       <c r="C25" t="s">
         <v>28</v>
       </c>
+      <c r="T25" t="s">
+        <v>5</v>
+      </c>
       <c r="U25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X25" t="s">
         <v>14</v>
       </c>
       <c r="AE25" t="s">
@@ -1589,20 +1562,23 @@
       <c r="C26" t="s">
         <v>29</v>
       </c>
+      <c r="T26" t="s">
+        <v>5</v>
+      </c>
       <c r="U26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V26" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="W26" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="X26" t="s">
         <v>11</v>
       </c>
       <c r="Y26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="s">
         <v>10</v>
@@ -1614,12 +1590,9 @@
         <v>10</v>
       </c>
       <c r="AC26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE26" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1633,15 +1606,18 @@
       <c r="C27" t="s">
         <v>30</v>
       </c>
+      <c r="U27" t="s">
+        <v>5</v>
+      </c>
       <c r="V27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="s">
-        <v>7</v>
-      </c>
-      <c r="X27" t="s">
         <v>26</v>
       </c>
+      <c r="AC27" t="s">
+        <v>10</v>
+      </c>
       <c r="AD27" t="s">
         <v>10</v>
       </c>
@@ -1649,9 +1625,6 @@
         <v>10</v>
       </c>
       <c r="AF27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG27" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1665,19 +1638,19 @@
       <c r="C28" t="s">
         <v>31</v>
       </c>
+      <c r="U28" t="s">
+        <v>5</v>
+      </c>
       <c r="V28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="s">
-        <v>7</v>
-      </c>
-      <c r="X28" t="s">
         <v>26</v>
       </c>
+      <c r="AF28" t="s">
+        <v>10</v>
+      </c>
       <c r="AG28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH28" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1691,22 +1664,22 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
+      <c r="V29" t="s">
+        <v>5</v>
+      </c>
       <c r="W29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="Y29" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1720,22 +1693,22 @@
       <c r="C30" t="s">
         <v>33</v>
       </c>
+      <c r="V30" t="s">
+        <v>5</v>
+      </c>
       <c r="W30" t="s">
-        <v>5</v>
-      </c>
-      <c r="X30" t="s">
         <v>7</v>
       </c>
       <c r="Y30" t="s">
         <v>26</v>
       </c>
+      <c r="Z30" t="s">
+        <v>10</v>
+      </c>
       <c r="AA30" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH30" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1749,10 +1722,10 @@
       <c r="C31" t="s">
         <v>28</v>
       </c>
+      <c r="W31" t="s">
+        <v>5</v>
+      </c>
       <c r="X31" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y31" t="s">
         <v>7</v>
       </c>
       <c r="Z31" t="s">
@@ -1761,7 +1734,7 @@
       <c r="AA31" t="s">
         <v>14</v>
       </c>
-      <c r="AI31" t="s">
+      <c r="AH31" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1775,10 +1748,10 @@
       <c r="C32" t="s">
         <v>29</v>
       </c>
+      <c r="W32" t="s">
+        <v>5</v>
+      </c>
       <c r="X32" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" t="s">
         <v>7</v>
       </c>
       <c r="Z32" t="s">
@@ -1791,7 +1764,7 @@
         <v>11</v>
       </c>
       <c r="AC32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD32" t="s">
         <v>10</v>
@@ -1803,12 +1776,9 @@
         <v>10</v>
       </c>
       <c r="AG32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI32" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1822,15 +1792,18 @@
       <c r="C33" t="s">
         <v>30</v>
       </c>
+      <c r="X33" t="s">
+        <v>5</v>
+      </c>
       <c r="Y33" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" t="s">
         <v>7</v>
       </c>
       <c r="AA33" t="s">
         <v>26</v>
       </c>
+      <c r="AG33" t="s">
+        <v>10</v>
+      </c>
       <c r="AH33" t="s">
         <v>10</v>
       </c>
@@ -1838,9 +1811,6 @@
         <v>10</v>
       </c>
       <c r="AJ33" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK33" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1854,28 +1824,19 @@
       <c r="C34" t="s">
         <v>31</v>
       </c>
+      <c r="X34" t="s">
+        <v>5</v>
+      </c>
       <c r="Y34" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z34" t="s">
         <v>7</v>
       </c>
       <c r="AA34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD34" t="s">
         <v>26</v>
       </c>
+      <c r="AJ34" t="s">
+        <v>10</v>
+      </c>
       <c r="AK34" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL34" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1889,22 +1850,19 @@
       <c r="C35" t="s">
         <v>32</v>
       </c>
+      <c r="Y35" t="s">
+        <v>5</v>
+      </c>
       <c r="Z35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL35" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK35" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1918,22 +1876,22 @@
       <c r="C36" t="s">
         <v>33</v>
       </c>
+      <c r="Y36" t="s">
+        <v>5</v>
+      </c>
       <c r="Z36" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE36" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB36" t="s">
         <v>26</v>
       </c>
-      <c r="AF36" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM36" t="s">
+      <c r="AC36" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL36" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1945,27 +1903,27 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>10</v>
       </c>
       <c r="AG37" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AH37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM37" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1977,27 +1935,30 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>7</v>
+        <v>36</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>26</v>
       </c>
       <c r="AI38" t="s">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>10</v>
       </c>
       <c r="AL38" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AM38" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO38" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2009,21 +1970,21 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>10</v>
       </c>
       <c r="AH39" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM39" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2035,18 +1996,18 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>10</v>
       </c>
       <c r="AH40" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP40" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN40" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2060,11 +2021,20 @@
       <c r="C41" t="s">
         <v>20</v>
       </c>
+      <c r="AF41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>16</v>
+      </c>
       <c r="AI41" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AJ41" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AK41" t="s">
         <v>10</v>
@@ -2073,12 +2043,9 @@
         <v>10</v>
       </c>
       <c r="AM41" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AN41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP41" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2092,18 +2059,21 @@
       <c r="C42" t="s">
         <v>21</v>
       </c>
+      <c r="AF42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>7</v>
+      </c>
       <c r="AI42" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AJ42" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL42" t="s">
         <v>26</v>
       </c>
+      <c r="AM42" t="s">
+        <v>10</v>
+      </c>
       <c r="AN42" t="s">
         <v>10</v>
       </c>
@@ -2111,9 +2081,6 @@
         <v>10</v>
       </c>
       <c r="AP42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AQ42" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2127,20 +2094,23 @@
       <c r="C43" t="s">
         <v>22</v>
       </c>
+      <c r="AG43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>7</v>
+      </c>
       <c r="AJ43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK43" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL43" t="s">
         <v>26</v>
       </c>
+      <c r="AP43" t="s">
+        <v>11</v>
+      </c>
       <c r="AQ43" t="s">
         <v>11</v>
       </c>
       <c r="AR43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS43" t="s">
         <v>10</v>
@@ -2152,6 +2122,9 @@
         <v>10</v>
       </c>
       <c r="AV43" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW43" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2165,11 +2138,17 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>5</v>
+      <c r="AG44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>7</v>
       </c>
       <c r="AK44" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>10</v>
       </c>
       <c r="AM44" t="s">
         <v>10</v>
@@ -2178,18 +2157,9 @@
         <v>10</v>
       </c>
       <c r="AO44" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP44" t="s">
-        <v>10</v>
-      </c>
-      <c r="AQ44" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW44" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2203,11 +2173,17 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
+      <c r="AH45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>7</v>
+      </c>
       <c r="AK45" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL45" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM45" t="s">
         <v>10</v>
@@ -2222,15 +2198,9 @@
         <v>10</v>
       </c>
       <c r="AQ45" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR45" t="s">
-        <v>10</v>
-      </c>
-      <c r="AS45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW45" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX45" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2244,19 +2214,19 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AK46" t="s">
-        <v>5</v>
+      <c r="AH46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>7</v>
       </c>
       <c r="AL46" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN46" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW46" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX46" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2270,22 +2240,22 @@
       <c r="C47" t="s">
         <v>18</v>
       </c>
+      <c r="AI47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>7</v>
+      </c>
       <c r="AL47" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AM47" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AN47" t="s">
-        <v>11</v>
-      </c>
-      <c r="AO47" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX47" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY47" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2299,19 +2269,19 @@
       <c r="C48" t="s">
         <v>27</v>
       </c>
-      <c r="AL48" t="s">
-        <v>5</v>
+      <c r="AI48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>7</v>
       </c>
       <c r="AM48" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO48" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX48" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY48" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2325,22 +2295,22 @@
       <c r="C49" t="s">
         <v>28</v>
       </c>
+      <c r="AJ49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>7</v>
+      </c>
       <c r="AM49" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AN49" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO49" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP49" t="s">
-        <v>10</v>
-      </c>
-      <c r="AQ49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY49" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ49" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2354,41 +2324,29 @@
       <c r="C50" t="s">
         <v>29</v>
       </c>
-      <c r="AM50" t="s">
-        <v>5</v>
+      <c r="AJ50" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>7</v>
       </c>
       <c r="AN50" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>10</v>
       </c>
       <c r="AP50" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AQ50" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AR50" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AS50" t="s">
-        <v>11</v>
-      </c>
-      <c r="AT50" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU50" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV50" t="s">
-        <v>10</v>
-      </c>
-      <c r="AW50" t="s">
-        <v>10</v>
-      </c>
-      <c r="AX50" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY50" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ50" t="s">
         <v>15</v>
@@ -2404,25 +2362,28 @@
       <c r="C51" t="s">
         <v>30</v>
       </c>
-      <c r="AN51" t="s">
-        <v>5</v>
+      <c r="AK51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>7</v>
       </c>
       <c r="AO51" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR51" t="s">
         <v>26</v>
       </c>
-      <c r="AZ51" t="s">
-        <v>10</v>
+      <c r="AS51" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>14</v>
       </c>
       <c r="BA51" t="s">
-        <v>10</v>
-      </c>
-      <c r="BB51" t="s">
-        <v>10</v>
-      </c>
-      <c r="BC51" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2436,19 +2397,22 @@
       <c r="C52" t="s">
         <v>31</v>
       </c>
-      <c r="AN52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO52" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS52" t="s">
+      <c r="AK52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP52" t="s">
         <v>26</v>
       </c>
-      <c r="BC52" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD52" t="s">
+      <c r="AV52" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW52" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA52" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2462,22 +2426,19 @@
       <c r="C53" t="s">
         <v>32</v>
       </c>
-      <c r="AO53" t="s">
-        <v>5</v>
+      <c r="AL53" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>7</v>
       </c>
       <c r="AP53" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS53" t="s">
-        <v>26</v>
-      </c>
-      <c r="AT53" t="s">
-        <v>10</v>
-      </c>
-      <c r="AU53" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD53" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB53" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2491,22 +2452,19 @@
       <c r="C54" t="s">
         <v>33</v>
       </c>
-      <c r="AO54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP54" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT54" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU54" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV54" t="s">
-        <v>14</v>
-      </c>
-      <c r="BE54" t="s">
+      <c r="AL54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB54" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2520,22 +2478,19 @@
       <c r="C55" t="s">
         <v>28</v>
       </c>
-      <c r="AP55" t="s">
-        <v>5</v>
+      <c r="AM55" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>7</v>
       </c>
       <c r="AQ55" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT55" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU55" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV55" t="s">
-        <v>14</v>
-      </c>
-      <c r="BE55" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC55" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2549,43 +2504,43 @@
       <c r="C56" t="s">
         <v>29</v>
       </c>
-      <c r="AP56" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ56" t="s">
-        <v>7</v>
+      <c r="AM56" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>11</v>
       </c>
       <c r="AU56" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AV56" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AW56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ56" t="s">
         <v>10</v>
       </c>
       <c r="BA56" t="s">
-        <v>10</v>
-      </c>
-      <c r="BB56" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BC56" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD56" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF56" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2599,25 +2554,25 @@
       <c r="C57" t="s">
         <v>30</v>
       </c>
-      <c r="AQ57" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR57" t="s">
-        <v>7</v>
-      </c>
-      <c r="AV57" t="s">
+      <c r="AN57" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO57" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS57" t="s">
         <v>26</v>
       </c>
+      <c r="BA57" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB57" t="s">
+        <v>10</v>
+      </c>
+      <c r="BC57" t="s">
+        <v>10</v>
+      </c>
       <c r="BD57" t="s">
-        <v>10</v>
-      </c>
-      <c r="BE57" t="s">
-        <v>10</v>
-      </c>
-      <c r="BF57" t="s">
-        <v>10</v>
-      </c>
-      <c r="BG57" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2631,19 +2586,19 @@
       <c r="C58" t="s">
         <v>31</v>
       </c>
-      <c r="AQ58" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR58" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW58" t="s">
+      <c r="AN58" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT58" t="s">
         <v>26</v>
       </c>
-      <c r="BG58" t="s">
-        <v>10</v>
-      </c>
-      <c r="BH58" t="s">
+      <c r="BD58" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE58" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2657,22 +2612,28 @@
       <c r="C59" t="s">
         <v>32</v>
       </c>
-      <c r="AR59" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS59" t="s">
-        <v>7</v>
+      <c r="AO59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT59" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU59" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>34</v>
       </c>
       <c r="AW59" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AX59" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY59" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH59" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE59" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2686,22 +2647,22 @@
       <c r="C60" t="s">
         <v>33</v>
       </c>
-      <c r="AR60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>7</v>
+      <c r="AO60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>26</v>
       </c>
       <c r="AX60" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AY60" t="s">
-        <v>10</v>
-      </c>
-      <c r="AZ60" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI60" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF60" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2715,10 +2676,10 @@
       <c r="C61" t="s">
         <v>28</v>
       </c>
-      <c r="AS61" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT61" t="s">
+      <c r="AP61" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ61" t="s">
         <v>7</v>
       </c>
       <c r="AX61" t="s">
@@ -2727,7 +2688,7 @@
       <c r="AY61" t="s">
         <v>14</v>
       </c>
-      <c r="BI61" t="s">
+      <c r="BF61" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2741,43 +2702,37 @@
       <c r="C62" t="s">
         <v>29</v>
       </c>
-      <c r="AS62" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT62" t="s">
-        <v>7</v>
+      <c r="AP62" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ62" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>26</v>
       </c>
       <c r="AY62" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ62" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="BA62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD62" t="s">
         <v>10</v>
       </c>
       <c r="BE62" t="s">
-        <v>10</v>
-      </c>
-      <c r="BF62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BG62" t="s">
-        <v>10</v>
-      </c>
-      <c r="BH62" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ62" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2791,25 +2746,25 @@
       <c r="C63" t="s">
         <v>30</v>
       </c>
-      <c r="AT63" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV63" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ63" t="s">
+      <c r="AQ63" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW63" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY63" t="s">
         <v>26</v>
       </c>
+      <c r="BE63" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>10</v>
+      </c>
+      <c r="BG63" t="s">
+        <v>10</v>
+      </c>
       <c r="BH63" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI63" t="s">
-        <v>10</v>
-      </c>
-      <c r="BJ63" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK63" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2823,28 +2778,19 @@
       <c r="C64" t="s">
         <v>31</v>
       </c>
-      <c r="AT64" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV64" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA64" t="s">
-        <v>16</v>
-      </c>
-      <c r="BB64" t="s">
-        <v>16</v>
-      </c>
-      <c r="BC64" t="s">
-        <v>16</v>
-      </c>
-      <c r="BD64" t="s">
+      <c r="AQ64" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW64" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY64" t="s">
         <v>26</v>
       </c>
-      <c r="BK64" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL64" t="s">
+      <c r="BH64" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI64" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2858,22 +2804,19 @@
       <c r="C65" t="s">
         <v>32</v>
       </c>
-      <c r="AV65" t="s">
-        <v>5</v>
-      </c>
       <c r="AW65" t="s">
-        <v>7</v>
-      </c>
-      <c r="BD65" t="s">
-        <v>26</v>
-      </c>
-      <c r="BE65" t="s">
-        <v>10</v>
-      </c>
-      <c r="BF65" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL65" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ65" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA65" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI65" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2887,22 +2830,22 @@
       <c r="C66" t="s">
         <v>33</v>
       </c>
-      <c r="AV66" t="s">
-        <v>5</v>
-      </c>
       <c r="AW66" t="s">
-        <v>7</v>
-      </c>
-      <c r="BE66" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ66" t="s">
         <v>26</v>
       </c>
-      <c r="BF66" t="s">
-        <v>10</v>
-      </c>
-      <c r="BG66" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM66" t="s">
+      <c r="BA66" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB66" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ66" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2914,27 +2857,27 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="BB67" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC67" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE67" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>10</v>
       </c>
       <c r="BG67" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH67" t="s">
-        <v>7</v>
-      </c>
-      <c r="BI67" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BJ67" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK67" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL67" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM67" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2946,27 +2889,30 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="BB68" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC68" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD68" t="s">
+        <v>26</v>
       </c>
       <c r="BG68" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BH68" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BI68" t="s">
-        <v>26</v>
-      </c>
-      <c r="BL68" t="s">
-        <v>10</v>
-      </c>
-      <c r="BM68" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN68" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO68" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2978,21 +2924,21 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
-      </c>
-      <c r="BH69" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI69" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ69" t="s">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="BC69" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE69" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>14</v>
       </c>
       <c r="BK69" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO69" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3004,21 +2950,21 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
-      </c>
-      <c r="BH70" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI70" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ70" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK70" t="s">
-        <v>14</v>
-      </c>
-      <c r="BP70" t="s">
+        <v>38</v>
+      </c>
+      <c r="BC70" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD70" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE70" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>14</v>
+      </c>
+      <c r="BL70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3032,25 +2978,31 @@
       <c r="C71" t="s">
         <v>20</v>
       </c>
+      <c r="BD71" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE71" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG71" t="s">
+        <v>11</v>
+      </c>
+      <c r="BH71" t="s">
+        <v>10</v>
+      </c>
       <c r="BI71" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BJ71" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BK71" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BL71" t="s">
-        <v>10</v>
-      </c>
-      <c r="BM71" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN71" t="s">
-        <v>14</v>
-      </c>
-      <c r="BP71" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3064,28 +3016,28 @@
       <c r="C72" t="s">
         <v>21</v>
       </c>
-      <c r="BI72" t="s">
-        <v>5</v>
-      </c>
-      <c r="BJ72" t="s">
-        <v>7</v>
+      <c r="BD72" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE72" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>16</v>
+      </c>
+      <c r="BH72" t="s">
+        <v>26</v>
       </c>
       <c r="BK72" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BL72" t="s">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="BM72" t="s">
+        <v>10</v>
       </c>
       <c r="BN72" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO72" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP72" t="s">
-        <v>10</v>
-      </c>
-      <c r="BQ72" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3099,17 +3051,26 @@
       <c r="C73" t="s">
         <v>22</v>
       </c>
-      <c r="BJ73" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK73" t="s">
-        <v>7</v>
-      </c>
-      <c r="BL73" t="s">
+      <c r="BE73" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH73" t="s">
         <v>26</v>
       </c>
+      <c r="BN73" t="s">
+        <v>11</v>
+      </c>
+      <c r="BO73" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP73" t="s">
+        <v>11</v>
+      </c>
       <c r="BQ73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR73" t="s">
         <v>10</v>
@@ -3121,9 +3082,6 @@
         <v>10</v>
       </c>
       <c r="BU73" t="s">
-        <v>10</v>
-      </c>
-      <c r="BV73" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3137,31 +3095,28 @@
       <c r="C74" t="s">
         <v>23</v>
       </c>
+      <c r="BE74" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI74" t="s">
+        <v>10</v>
+      </c>
       <c r="BJ74" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BK74" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="BL74" t="s">
+        <v>10</v>
       </c>
       <c r="BM74" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN74" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO74" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP74" t="s">
-        <v>10</v>
-      </c>
-      <c r="BQ74" t="s">
-        <v>38</v>
-      </c>
-      <c r="BR74" t="s">
-        <v>14</v>
-      </c>
-      <c r="BV74" t="s">
+        <v>14</v>
+      </c>
+      <c r="BU74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3175,11 +3130,23 @@
       <c r="C75" t="s">
         <v>24</v>
       </c>
+      <c r="BF75" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG75" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI75" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ75" t="s">
+        <v>10</v>
+      </c>
       <c r="BK75" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BL75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BM75" t="s">
         <v>10</v>
@@ -3188,21 +3155,9 @@
         <v>10</v>
       </c>
       <c r="BO75" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP75" t="s">
-        <v>10</v>
-      </c>
-      <c r="BQ75" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR75" t="s">
-        <v>10</v>
-      </c>
-      <c r="BS75" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW75" t="s">
+        <v>14</v>
+      </c>
+      <c r="BV75" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3216,19 +3171,19 @@
       <c r="C76" t="s">
         <v>25</v>
       </c>
+      <c r="BF76" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG76" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ76" t="s">
+        <v>10</v>
+      </c>
       <c r="BK76" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL76" t="s">
-        <v>7</v>
-      </c>
-      <c r="BN76" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO76" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW76" t="s">
+        <v>14</v>
+      </c>
+      <c r="BV76" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3242,22 +3197,22 @@
       <c r="C77" t="s">
         <v>18</v>
       </c>
+      <c r="BG77" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH77" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ77" t="s">
+        <v>11</v>
+      </c>
+      <c r="BK77" t="s">
+        <v>10</v>
+      </c>
       <c r="BL77" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM77" t="s">
-        <v>7</v>
-      </c>
-      <c r="BN77" t="s">
-        <v>11</v>
-      </c>
-      <c r="BO77" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP77" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX77" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW77" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3271,19 +3226,19 @@
       <c r="C78" t="s">
         <v>27</v>
       </c>
+      <c r="BG78" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH78" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK78" t="s">
+        <v>10</v>
+      </c>
       <c r="BL78" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM78" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO78" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP78" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX78" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW78" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3297,22 +3252,22 @@
       <c r="C79" t="s">
         <v>28</v>
       </c>
+      <c r="BH79" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI79" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK79" t="s">
+        <v>11</v>
+      </c>
+      <c r="BL79" t="s">
+        <v>10</v>
+      </c>
       <c r="BM79" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN79" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO79" t="s">
-        <v>26</v>
-      </c>
-      <c r="BP79" t="s">
-        <v>10</v>
-      </c>
-      <c r="BQ79" t="s">
-        <v>14</v>
-      </c>
-      <c r="BY79" t="s">
+        <v>14</v>
+      </c>
+      <c r="BX79" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3326,43 +3281,31 @@
       <c r="C80" t="s">
         <v>29</v>
       </c>
+      <c r="BH80" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL80" t="s">
+        <v>16</v>
+      </c>
       <c r="BM80" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BN80" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="BO80" t="s">
+        <v>10</v>
       </c>
       <c r="BP80" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BQ80" t="s">
-        <v>16</v>
-      </c>
-      <c r="BR80" t="s">
-        <v>26</v>
-      </c>
-      <c r="BS80" t="s">
-        <v>11</v>
-      </c>
-      <c r="BT80" t="s">
-        <v>11</v>
-      </c>
-      <c r="BU80" t="s">
-        <v>11</v>
-      </c>
-      <c r="BV80" t="s">
-        <v>10</v>
-      </c>
-      <c r="BW80" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX80" t="s">
-        <v>10</v>
-      </c>
-      <c r="BY80" t="s">
-        <v>10</v>
-      </c>
-      <c r="BZ80" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3376,25 +3319,28 @@
       <c r="C81" t="s">
         <v>30</v>
       </c>
-      <c r="BN81" t="s">
-        <v>5</v>
-      </c>
-      <c r="BO81" t="s">
-        <v>7</v>
+      <c r="BI81" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM81" t="s">
+        <v>26</v>
+      </c>
+      <c r="BQ81" t="s">
+        <v>10</v>
       </c>
       <c r="BR81" t="s">
-        <v>26</v>
-      </c>
-      <c r="BZ81" t="s">
-        <v>10</v>
-      </c>
-      <c r="CA81" t="s">
-        <v>10</v>
-      </c>
-      <c r="CB81" t="s">
-        <v>10</v>
-      </c>
-      <c r="CC81" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS81" t="s">
+        <v>10</v>
+      </c>
+      <c r="BT81" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY81" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3408,19 +3354,22 @@
       <c r="C82" t="s">
         <v>31</v>
       </c>
+      <c r="BI82" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>7</v>
+      </c>
       <c r="BN82" t="s">
-        <v>5</v>
-      </c>
-      <c r="BO82" t="s">
-        <v>7</v>
-      </c>
-      <c r="BS82" t="s">
         <v>26</v>
       </c>
-      <c r="CC82" t="s">
-        <v>10</v>
-      </c>
-      <c r="CD82" t="s">
+      <c r="BT82" t="s">
+        <v>10</v>
+      </c>
+      <c r="BU82" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY82" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3434,22 +3383,19 @@
       <c r="C83" t="s">
         <v>32</v>
       </c>
+      <c r="BJ83" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK83" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN83" t="s">
+        <v>10</v>
+      </c>
       <c r="BO83" t="s">
-        <v>5</v>
-      </c>
-      <c r="BP83" t="s">
-        <v>7</v>
-      </c>
-      <c r="BS83" t="s">
-        <v>26</v>
-      </c>
-      <c r="BT83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BU83" t="s">
-        <v>14</v>
-      </c>
-      <c r="CD83" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ83" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3463,22 +3409,19 @@
       <c r="C84" t="s">
         <v>33</v>
       </c>
+      <c r="BJ84" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK84" t="s">
+        <v>7</v>
+      </c>
       <c r="BO84" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BP84" t="s">
-        <v>7</v>
-      </c>
-      <c r="BT84" t="s">
-        <v>26</v>
-      </c>
-      <c r="BU84" t="s">
-        <v>10</v>
-      </c>
-      <c r="BV84" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE84" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ84" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3492,22 +3435,19 @@
       <c r="C85" t="s">
         <v>28</v>
       </c>
+      <c r="BK85" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL85" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO85" t="s">
+        <v>10</v>
+      </c>
       <c r="BP85" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ85" t="s">
-        <v>7</v>
-      </c>
-      <c r="BT85" t="s">
-        <v>26</v>
-      </c>
-      <c r="BU85" t="s">
-        <v>10</v>
-      </c>
-      <c r="BV85" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE85" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA85" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3521,43 +3461,43 @@
       <c r="C86" t="s">
         <v>29</v>
       </c>
+      <c r="BK86" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL86" t="s">
+        <v>7</v>
+      </c>
       <c r="BP86" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BQ86" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="BR86" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS86" t="s">
+        <v>11</v>
+      </c>
+      <c r="BT86" t="s">
+        <v>11</v>
       </c>
       <c r="BU86" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BV86" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BW86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BY86" t="s">
-        <v>11</v>
-      </c>
-      <c r="BZ86" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CA86" t="s">
-        <v>10</v>
-      </c>
-      <c r="CB86" t="s">
-        <v>10</v>
-      </c>
-      <c r="CC86" t="s">
-        <v>10</v>
-      </c>
-      <c r="CD86" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF86" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3571,25 +3511,25 @@
       <c r="C87" t="s">
         <v>30</v>
       </c>
+      <c r="BL87" t="s">
+        <v>5</v>
+      </c>
+      <c r="BM87" t="s">
+        <v>7</v>
+      </c>
       <c r="BQ87" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR87" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV87" t="s">
         <v>26</v>
       </c>
-      <c r="CD87" t="s">
-        <v>10</v>
-      </c>
-      <c r="CE87" t="s">
-        <v>10</v>
-      </c>
-      <c r="CF87" t="s">
-        <v>10</v>
-      </c>
-      <c r="CG87" t="s">
+      <c r="BY87" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ87" t="s">
+        <v>10</v>
+      </c>
+      <c r="CA87" t="s">
+        <v>10</v>
+      </c>
+      <c r="CB87" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3603,19 +3543,19 @@
       <c r="C88" t="s">
         <v>31</v>
       </c>
-      <c r="BQ88" t="s">
-        <v>5</v>
+      <c r="BL88" t="s">
+        <v>5</v>
+      </c>
+      <c r="BM88" t="s">
+        <v>7</v>
       </c>
       <c r="BR88" t="s">
-        <v>7</v>
-      </c>
-      <c r="BW88" t="s">
         <v>26</v>
       </c>
-      <c r="CG88" t="s">
-        <v>10</v>
-      </c>
-      <c r="CH88" t="s">
+      <c r="CB88" t="s">
+        <v>10</v>
+      </c>
+      <c r="CC88" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3629,22 +3569,28 @@
       <c r="C89" t="s">
         <v>32</v>
       </c>
+      <c r="BM89" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN89" t="s">
+        <v>7</v>
+      </c>
       <c r="BR89" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BS89" t="s">
-        <v>7</v>
-      </c>
-      <c r="BW89" t="s">
-        <v>26</v>
-      </c>
-      <c r="BX89" t="s">
-        <v>10</v>
-      </c>
-      <c r="BY89" t="s">
-        <v>14</v>
-      </c>
-      <c r="CH89" t="s">
+        <v>34</v>
+      </c>
+      <c r="BT89" t="s">
+        <v>34</v>
+      </c>
+      <c r="BU89" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV89" t="s">
+        <v>14</v>
+      </c>
+      <c r="CC89" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3658,22 +3604,22 @@
       <c r="C90" t="s">
         <v>33</v>
       </c>
-      <c r="BR90" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS90" t="s">
-        <v>7</v>
-      </c>
-      <c r="BX90" t="s">
+      <c r="BM90" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN90" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU90" t="s">
         <v>26</v>
       </c>
-      <c r="BY90" t="s">
-        <v>10</v>
-      </c>
-      <c r="BZ90" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI90" t="s">
+      <c r="BV90" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW90" t="s">
+        <v>14</v>
+      </c>
+      <c r="CD90" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3687,19 +3633,19 @@
       <c r="C91" t="s">
         <v>28</v>
       </c>
-      <c r="BS91" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT91" t="s">
-        <v>7</v>
-      </c>
-      <c r="BX91" t="s">
-        <v>10</v>
-      </c>
-      <c r="BY91" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI91" t="s">
+      <c r="BN91" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO91" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV91" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW91" t="s">
+        <v>14</v>
+      </c>
+      <c r="CD91" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3713,43 +3659,37 @@
       <c r="C92" t="s">
         <v>29</v>
       </c>
-      <c r="BS92" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT92" t="s">
-        <v>7</v>
+      <c r="BN92" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO92" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV92" t="s">
+        <v>26</v>
+      </c>
+      <c r="BW92" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX92" t="s">
+        <v>11</v>
       </c>
       <c r="BY92" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BZ92" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="CA92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CC92" t="s">
-        <v>11</v>
-      </c>
-      <c r="CD92" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CE92" t="s">
-        <v>10</v>
-      </c>
-      <c r="CF92" t="s">
-        <v>10</v>
-      </c>
-      <c r="CG92" t="s">
-        <v>10</v>
-      </c>
-      <c r="CH92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ92" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3763,25 +3703,25 @@
       <c r="C93" t="s">
         <v>30</v>
       </c>
-      <c r="BT93" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV93" t="s">
-        <v>7</v>
-      </c>
-      <c r="BZ93" t="s">
+      <c r="BO93" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU93" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW93" t="s">
         <v>26</v>
       </c>
-      <c r="CH93" t="s">
-        <v>10</v>
-      </c>
-      <c r="CI93" t="s">
-        <v>10</v>
-      </c>
-      <c r="CJ93" t="s">
-        <v>10</v>
-      </c>
-      <c r="CK93" t="s">
+      <c r="CC93" t="s">
+        <v>10</v>
+      </c>
+      <c r="CD93" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE93" t="s">
+        <v>10</v>
+      </c>
+      <c r="CF93" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3795,28 +3735,19 @@
       <c r="C94" t="s">
         <v>31</v>
       </c>
-      <c r="BT94" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV94" t="s">
-        <v>7</v>
-      </c>
-      <c r="CA94" t="s">
-        <v>16</v>
-      </c>
-      <c r="CB94" t="s">
-        <v>16</v>
-      </c>
-      <c r="CC94" t="s">
-        <v>16</v>
-      </c>
-      <c r="CD94" t="s">
+      <c r="BO94" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU94" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW94" t="s">
         <v>26</v>
       </c>
-      <c r="CK94" t="s">
-        <v>10</v>
-      </c>
-      <c r="CL94" t="s">
+      <c r="CF94" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG94" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3830,22 +3761,19 @@
       <c r="C95" t="s">
         <v>32</v>
       </c>
+      <c r="BU95" t="s">
+        <v>5</v>
+      </c>
       <c r="BV95" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW95" t="s">
-        <v>7</v>
-      </c>
-      <c r="CD95" t="s">
-        <v>26</v>
-      </c>
-      <c r="CE95" t="s">
-        <v>10</v>
-      </c>
-      <c r="CF95" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL95" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX95" t="s">
+        <v>10</v>
+      </c>
+      <c r="BY95" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG95" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3859,22 +3787,22 @@
       <c r="C96" t="s">
         <v>33</v>
       </c>
+      <c r="BU96" t="s">
+        <v>5</v>
+      </c>
       <c r="BV96" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW96" t="s">
-        <v>7</v>
-      </c>
-      <c r="CE96" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX96" t="s">
         <v>26</v>
       </c>
-      <c r="CF96" t="s">
-        <v>10</v>
-      </c>
-      <c r="CG96" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM96" t="s">
+      <c r="BY96" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ96" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH96" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3886,27 +3814,27 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
-      </c>
-      <c r="CG97" t="s">
-        <v>5</v>
+        <v>35</v>
+      </c>
+      <c r="BZ97" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA97" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB97" t="s">
+        <v>10</v>
+      </c>
+      <c r="CC97" t="s">
+        <v>10</v>
+      </c>
+      <c r="CD97" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE97" t="s">
+        <v>14</v>
       </c>
       <c r="CH97" t="s">
-        <v>7</v>
-      </c>
-      <c r="CI97" t="s">
-        <v>10</v>
-      </c>
-      <c r="CJ97" t="s">
-        <v>10</v>
-      </c>
-      <c r="CK97" t="s">
-        <v>10</v>
-      </c>
-      <c r="CL97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM97" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3918,27 +3846,30 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="BZ98" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA98" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB98" t="s">
+        <v>26</v>
+      </c>
+      <c r="CE98" t="s">
+        <v>10</v>
+      </c>
+      <c r="CF98" t="s">
+        <v>10</v>
       </c>
       <c r="CG98" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CH98" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="CI98" t="s">
-        <v>26</v>
-      </c>
-      <c r="CL98" t="s">
-        <v>10</v>
-      </c>
-      <c r="CM98" t="s">
-        <v>10</v>
-      </c>
-      <c r="CN98" t="s">
-        <v>10</v>
-      </c>
-      <c r="CO98" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3950,21 +3881,21 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
-      </c>
-      <c r="CH99" t="s">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="CA99" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB99" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC99" t="s">
+        <v>10</v>
+      </c>
+      <c r="CD99" t="s">
+        <v>14</v>
       </c>
       <c r="CI99" t="s">
-        <v>7</v>
-      </c>
-      <c r="CJ99" t="s">
-        <v>10</v>
-      </c>
-      <c r="CK99" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO99" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3976,18 +3907,18 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
-      </c>
-      <c r="CH100" t="s">
-        <v>5</v>
+        <v>38</v>
+      </c>
+      <c r="CA100" t="s">
+        <v>5</v>
+      </c>
+      <c r="CC100" t="s">
+        <v>10</v>
+      </c>
+      <c r="CD100" t="s">
+        <v>14</v>
       </c>
       <c r="CJ100" t="s">
-        <v>10</v>
-      </c>
-      <c r="CK100" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP100" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4001,22 +3932,19 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="CI101" t="s">
-        <v>5</v>
+      <c r="CB101" t="s">
+        <v>5</v>
+      </c>
+      <c r="CC101" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD101" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE101" t="s">
+        <v>14</v>
       </c>
       <c r="CJ101" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK101" t="s">
-        <v>11</v>
-      </c>
-      <c r="CL101" t="s">
-        <v>10</v>
-      </c>
-      <c r="CM101" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP101" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4030,25 +3958,22 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="CI102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CJ102" t="s">
-        <v>7</v>
+      <c r="CB102" t="s">
+        <v>5</v>
+      </c>
+      <c r="CC102" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD102" t="s">
+        <v>16</v>
+      </c>
+      <c r="CE102" t="s">
+        <v>10</v>
+      </c>
+      <c r="CF102" t="s">
+        <v>14</v>
       </c>
       <c r="CK102" t="s">
-        <v>16</v>
-      </c>
-      <c r="CL102" t="s">
-        <v>11</v>
-      </c>
-      <c r="CM102" t="s">
-        <v>10</v>
-      </c>
-      <c r="CN102" t="s">
-        <v>14</v>
-      </c>
-      <c r="CQ102" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4062,25 +3987,25 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="CJ103" t="s">
-        <v>5</v>
+      <c r="CC103" t="s">
+        <v>5</v>
+      </c>
+      <c r="CD103" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE103" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF103" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG103" t="s">
+        <v>10</v>
+      </c>
+      <c r="CH103" t="s">
+        <v>14</v>
       </c>
       <c r="CK103" t="s">
-        <v>7</v>
-      </c>
-      <c r="CL103" t="s">
-        <v>16</v>
-      </c>
-      <c r="CM103" t="s">
-        <v>11</v>
-      </c>
-      <c r="CN103" t="s">
-        <v>10</v>
-      </c>
-      <c r="CO103" t="s">
-        <v>14</v>
-      </c>
-      <c r="CQ103" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4094,25 +4019,25 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="CJ104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK104" t="s">
-        <v>7</v>
-      </c>
-      <c r="CM104" t="s">
+      <c r="CC104" t="s">
+        <v>5</v>
+      </c>
+      <c r="CD104" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF104" t="s">
         <v>16</v>
       </c>
-      <c r="CN104" t="s">
-        <v>11</v>
-      </c>
-      <c r="CO104" t="s">
-        <v>10</v>
-      </c>
-      <c r="CP104" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR104" t="s">
+      <c r="CG104" t="s">
+        <v>11</v>
+      </c>
+      <c r="CH104" t="s">
+        <v>10</v>
+      </c>
+      <c r="CI104" t="s">
+        <v>14</v>
+      </c>
+      <c r="CL104" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4126,25 +4051,25 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="CK105" t="s">
-        <v>5</v>
+      <c r="CD105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE105" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG105" t="s">
+        <v>16</v>
+      </c>
+      <c r="CH105" t="s">
+        <v>11</v>
+      </c>
+      <c r="CI105" t="s">
+        <v>10</v>
+      </c>
+      <c r="CJ105" t="s">
+        <v>14</v>
       </c>
       <c r="CL105" t="s">
-        <v>7</v>
-      </c>
-      <c r="CN105" t="s">
-        <v>16</v>
-      </c>
-      <c r="CO105" t="s">
-        <v>11</v>
-      </c>
-      <c r="CP105" t="s">
-        <v>10</v>
-      </c>
-      <c r="CQ105" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR105" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4158,25 +4083,25 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
+      <c r="CD106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE106" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH106" t="s">
+        <v>16</v>
+      </c>
+      <c r="CI106" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ106" t="s">
+        <v>10</v>
+      </c>
       <c r="CK106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CL106" t="s">
-        <v>7</v>
-      </c>
-      <c r="CO106" t="s">
-        <v>16</v>
-      </c>
-      <c r="CP106" t="s">
-        <v>11</v>
-      </c>
-      <c r="CQ106" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR106" t="s">
-        <v>14</v>
-      </c>
-      <c r="CS106" t="s">
+        <v>14</v>
+      </c>
+      <c r="CM106" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4190,22 +4115,25 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
+      <c r="CE107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF107" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI107" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ107" t="s">
+        <v>11</v>
+      </c>
+      <c r="CK107" t="s">
+        <v>10</v>
+      </c>
       <c r="CL107" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CM107" t="s">
-        <v>7</v>
-      </c>
-      <c r="CP107" t="s">
-        <v>16</v>
-      </c>
-      <c r="CQ107" t="s">
-        <v>11</v>
-      </c>
-      <c r="CR107" t="s">
-        <v>10</v>
-      </c>
-      <c r="CS107" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4219,22 +4147,25 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
+      <c r="CE108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF108" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ108" t="s">
+        <v>16</v>
+      </c>
+      <c r="CK108" t="s">
+        <v>11</v>
+      </c>
       <c r="CL108" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CM108" t="s">
-        <v>7</v>
-      </c>
-      <c r="CQ108" t="s">
-        <v>16</v>
-      </c>
-      <c r="CR108" t="s">
-        <v>11</v>
-      </c>
-      <c r="CS108" t="s">
-        <v>10</v>
-      </c>
-      <c r="CT108" t="s">
+        <v>14</v>
+      </c>
+      <c r="CN108" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4248,22 +4179,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
+      <c r="CF109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CG109" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK109" t="s">
+        <v>16</v>
+      </c>
+      <c r="CL109" t="s">
+        <v>11</v>
+      </c>
       <c r="CM109" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CN109" t="s">
-        <v>7</v>
-      </c>
-      <c r="CR109" t="s">
-        <v>16</v>
-      </c>
-      <c r="CS109" t="s">
-        <v>11</v>
-      </c>
-      <c r="CT109" t="s">
-        <v>10</v>
-      </c>
-      <c r="CU109" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4330,15 +4261,15 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
         <v>56</v>
-      </c>
-      <c r="B119" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B120" t="s">
         <v>58</v>

--- a/project/outputs_xlsx_solution/test33.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/test33.2-wide.xlsx
@@ -846,6 +846,12 @@
       <c r="CN1">
         <v>89</v>
       </c>
+      <c r="CO1">
+        <v>90</v>
+      </c>
+      <c r="CP1">
+        <v>91</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -2001,6 +2007,9 @@
       <c r="AE40" t="s">
         <v>5</v>
       </c>
+      <c r="AF40" t="s">
+        <v>7</v>
+      </c>
       <c r="AG40" t="s">
         <v>10</v>
       </c>
@@ -2021,17 +2030,11 @@
       <c r="C41" t="s">
         <v>20</v>
       </c>
-      <c r="AF41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>7</v>
-      </c>
       <c r="AH41" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AI41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AJ41" t="s">
         <v>10</v>
@@ -2059,14 +2062,11 @@
       <c r="C42" t="s">
         <v>21</v>
       </c>
-      <c r="AF42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>7</v>
+      <c r="AH42" t="s">
+        <v>5</v>
       </c>
       <c r="AI42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AJ42" t="s">
         <v>26</v>
@@ -2094,13 +2094,13 @@
       <c r="C43" t="s">
         <v>22</v>
       </c>
-      <c r="AG43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" t="s">
-        <v>7</v>
+      <c r="AI43" t="s">
+        <v>5</v>
       </c>
       <c r="AJ43" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK43" t="s">
         <v>26</v>
       </c>
       <c r="AP43" t="s">
@@ -2138,10 +2138,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AG44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" t="s">
+      <c r="AI44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" t="s">
         <v>7</v>
       </c>
       <c r="AK44" t="s">
@@ -2173,14 +2173,11 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AH45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>7</v>
+      <c r="AJ45" t="s">
+        <v>5</v>
       </c>
       <c r="AK45" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL45" t="s">
         <v>10</v>
@@ -2198,6 +2195,9 @@
         <v>10</v>
       </c>
       <c r="AQ45" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR45" t="s">
         <v>14</v>
       </c>
       <c r="AX45" t="s">
@@ -2214,10 +2214,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AH46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" t="s">
+      <c r="AJ46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" t="s">
         <v>7</v>
       </c>
       <c r="AL46" t="s">
@@ -2240,14 +2240,11 @@
       <c r="C47" t="s">
         <v>18</v>
       </c>
-      <c r="AI47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>7</v>
+      <c r="AK47" t="s">
+        <v>5</v>
       </c>
       <c r="AL47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AM47" t="s">
         <v>10</v>
@@ -2269,10 +2266,10 @@
       <c r="C48" t="s">
         <v>27</v>
       </c>
-      <c r="AI48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" t="s">
+      <c r="AK48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" t="s">
         <v>7</v>
       </c>
       <c r="AM48" t="s">
@@ -2295,14 +2292,11 @@
       <c r="C49" t="s">
         <v>28</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" t="s">
-        <v>7</v>
+      <c r="AL49" t="s">
+        <v>5</v>
       </c>
       <c r="AM49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AN49" t="s">
         <v>10</v>
@@ -2324,10 +2318,10 @@
       <c r="C50" t="s">
         <v>29</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK50" t="s">
+      <c r="AL50" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM50" t="s">
         <v>7</v>
       </c>
       <c r="AN50" t="s">
@@ -2362,10 +2356,10 @@
       <c r="C51" t="s">
         <v>30</v>
       </c>
-      <c r="AK51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL51" t="s">
+      <c r="AM51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN51" t="s">
         <v>7</v>
       </c>
       <c r="AO51" t="s">
@@ -2397,10 +2391,10 @@
       <c r="C52" t="s">
         <v>31</v>
       </c>
-      <c r="AK52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL52" t="s">
+      <c r="AM52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" t="s">
         <v>7</v>
       </c>
       <c r="AP52" t="s">
@@ -2426,10 +2420,10 @@
       <c r="C53" t="s">
         <v>32</v>
       </c>
-      <c r="AL53" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM53" t="s">
+      <c r="AN53" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO53" t="s">
         <v>7</v>
       </c>
       <c r="AP53" t="s">
@@ -2452,10 +2446,10 @@
       <c r="C54" t="s">
         <v>33</v>
       </c>
-      <c r="AL54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM54" t="s">
+      <c r="AN54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO54" t="s">
         <v>7</v>
       </c>
       <c r="AQ54" t="s">
@@ -2478,10 +2472,10 @@
       <c r="C55" t="s">
         <v>28</v>
       </c>
-      <c r="AM55" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN55" t="s">
+      <c r="AO55" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP55" t="s">
         <v>7</v>
       </c>
       <c r="AQ55" t="s">
@@ -2504,10 +2498,10 @@
       <c r="C56" t="s">
         <v>29</v>
       </c>
-      <c r="AM56" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN56" t="s">
+      <c r="AO56" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP56" t="s">
         <v>7</v>
       </c>
       <c r="AR56" t="s">
@@ -2554,10 +2548,10 @@
       <c r="C57" t="s">
         <v>30</v>
       </c>
-      <c r="AN57" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO57" t="s">
+      <c r="AP57" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ57" t="s">
         <v>7</v>
       </c>
       <c r="AS57" t="s">
@@ -2586,10 +2580,10 @@
       <c r="C58" t="s">
         <v>31</v>
       </c>
-      <c r="AN58" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO58" t="s">
+      <c r="AP58" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ58" t="s">
         <v>7</v>
       </c>
       <c r="AT58" t="s">
@@ -2612,10 +2606,10 @@
       <c r="C59" t="s">
         <v>32</v>
       </c>
-      <c r="AO59" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP59" t="s">
+      <c r="AQ59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR59" t="s">
         <v>7</v>
       </c>
       <c r="AT59" t="s">
@@ -2647,10 +2641,10 @@
       <c r="C60" t="s">
         <v>33</v>
       </c>
-      <c r="AO60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP60" t="s">
+      <c r="AQ60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR60" t="s">
         <v>7</v>
       </c>
       <c r="AW60" t="s">
@@ -2676,10 +2670,10 @@
       <c r="C61" t="s">
         <v>28</v>
       </c>
-      <c r="AP61" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ61" t="s">
+      <c r="AR61" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS61" t="s">
         <v>7</v>
       </c>
       <c r="AX61" t="s">
@@ -2702,10 +2696,10 @@
       <c r="C62" t="s">
         <v>29</v>
       </c>
-      <c r="AP62" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ62" t="s">
+      <c r="AR62" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS62" t="s">
         <v>7</v>
       </c>
       <c r="AX62" t="s">
@@ -2746,7 +2740,7 @@
       <c r="C63" t="s">
         <v>30</v>
       </c>
-      <c r="AQ63" t="s">
+      <c r="AS63" t="s">
         <v>5</v>
       </c>
       <c r="AW63" t="s">
@@ -2778,7 +2772,7 @@
       <c r="C64" t="s">
         <v>31</v>
       </c>
-      <c r="AQ64" t="s">
+      <c r="AS64" t="s">
         <v>5</v>
       </c>
       <c r="AW64" t="s">
@@ -3912,6 +3906,9 @@
       <c r="CA100" t="s">
         <v>5</v>
       </c>
+      <c r="CB100" t="s">
+        <v>7</v>
+      </c>
       <c r="CC100" t="s">
         <v>10</v>
       </c>
@@ -3932,16 +3929,19 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="CB101" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC101" t="s">
-        <v>7</v>
-      </c>
       <c r="CD101" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CE101" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF101" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG101" t="s">
+        <v>10</v>
+      </c>
+      <c r="CH101" t="s">
         <v>14</v>
       </c>
       <c r="CJ101" t="s">
@@ -3958,19 +3958,22 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="CB102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC102" t="s">
-        <v>7</v>
-      </c>
       <c r="CD102" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE102" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF102" t="s">
         <v>16</v>
       </c>
-      <c r="CE102" t="s">
-        <v>10</v>
-      </c>
-      <c r="CF102" t="s">
+      <c r="CG102" t="s">
+        <v>11</v>
+      </c>
+      <c r="CH102" t="s">
+        <v>10</v>
+      </c>
+      <c r="CI102" t="s">
         <v>14</v>
       </c>
       <c r="CK102" t="s">
@@ -3987,22 +3990,22 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="CC103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD103" t="s">
-        <v>7</v>
-      </c>
       <c r="CE103" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF103" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG103" t="s">
         <v>16</v>
       </c>
-      <c r="CF103" t="s">
-        <v>11</v>
-      </c>
-      <c r="CG103" t="s">
-        <v>10</v>
-      </c>
       <c r="CH103" t="s">
+        <v>11</v>
+      </c>
+      <c r="CI103" t="s">
+        <v>10</v>
+      </c>
+      <c r="CJ103" t="s">
         <v>14</v>
       </c>
       <c r="CK103" t="s">
@@ -4019,22 +4022,22 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="CC104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD104" t="s">
-        <v>7</v>
+      <c r="CE104" t="s">
+        <v>5</v>
       </c>
       <c r="CF104" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH104" t="s">
         <v>16</v>
       </c>
-      <c r="CG104" t="s">
-        <v>11</v>
-      </c>
-      <c r="CH104" t="s">
-        <v>10</v>
-      </c>
       <c r="CI104" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ104" t="s">
+        <v>10</v>
+      </c>
+      <c r="CK104" t="s">
         <v>14</v>
       </c>
       <c r="CL104" t="s">
@@ -4051,23 +4054,20 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="CD105" t="s">
-        <v>5</v>
-      </c>
-      <c r="CE105" t="s">
-        <v>7</v>
+      <c r="CF105" t="s">
+        <v>5</v>
       </c>
       <c r="CG105" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI105" t="s">
         <v>16</v>
       </c>
-      <c r="CH105" t="s">
-        <v>11</v>
-      </c>
-      <c r="CI105" t="s">
-        <v>10</v>
-      </c>
       <c r="CJ105" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="CK105" t="s">
+        <v>10</v>
       </c>
       <c r="CL105" t="s">
         <v>15</v>
@@ -4083,23 +4083,20 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="CD106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CE106" t="s">
-        <v>7</v>
-      </c>
-      <c r="CH106" t="s">
+      <c r="CF106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CG106" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ106" t="s">
         <v>16</v>
       </c>
-      <c r="CI106" t="s">
-        <v>11</v>
-      </c>
-      <c r="CJ106" t="s">
-        <v>10</v>
-      </c>
       <c r="CK106" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="CL106" t="s">
+        <v>10</v>
       </c>
       <c r="CM106" t="s">
         <v>15</v>
@@ -4115,25 +4112,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="CE107" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF107" t="s">
-        <v>7</v>
-      </c>
-      <c r="CI107" t="s">
+      <c r="CG107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CH107" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK107" t="s">
         <v>16</v>
       </c>
-      <c r="CJ107" t="s">
-        <v>11</v>
-      </c>
-      <c r="CK107" t="s">
-        <v>10</v>
-      </c>
       <c r="CL107" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CM107" t="s">
+        <v>10</v>
+      </c>
+      <c r="CN107" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4147,25 +4141,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="CE108" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF108" t="s">
-        <v>7</v>
-      </c>
-      <c r="CJ108" t="s">
+      <c r="CG108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CH108" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL108" t="s">
         <v>16</v>
       </c>
-      <c r="CK108" t="s">
-        <v>11</v>
-      </c>
-      <c r="CL108" t="s">
-        <v>10</v>
-      </c>
       <c r="CM108" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CN108" t="s">
+        <v>10</v>
+      </c>
+      <c r="CO108" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4179,22 +4170,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="CF109" t="s">
-        <v>5</v>
-      </c>
-      <c r="CG109" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK109" t="s">
+      <c r="CH109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI109" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM109" t="s">
         <v>16</v>
       </c>
-      <c r="CL109" t="s">
-        <v>11</v>
-      </c>
-      <c r="CM109" t="s">
-        <v>10</v>
-      </c>
       <c r="CN109" t="s">
+        <v>11</v>
+      </c>
+      <c r="CO109" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP109" t="s">
         <v>15</v>
       </c>
     </row>
